--- a/codecoin_database.xlsx
+++ b/codecoin_database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="spaces" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="events" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bugjam" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="spaces" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="events" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="bugjam" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1172,449 +1172,2723 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>คลังคำถาม | level: 1=ตอนซื้อ(ง่าย) 2=อัปเกรดชำนาญ 3=อัปเกรดผู้เชี่ยวชาญ | answer กรอก a/b/c/d ตัวเดียว | time_limit วินาที (เว้นว่าง=ไม่จับเวลา) | แถวยังไม่เสร็จใส่ DRAFT หน้าโจทย์</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>question_id</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>space_id</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>question_th</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>choice_a</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>choice_b</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>choice_c</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>choice_d</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>time_limit</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>coding_01_L1_01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>coding_01</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HTML ทำหน้าที่อะไรบนหน้าเว็บ?</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ตกแต่งสีสัน</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>เป็นโครงสร้างของหน้าเว็บ</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>คำนวณตัวเลข</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>coding_01_L1_02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coding_01</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ถ้า HTML คือโครงบ้าน แล้ว CSS เปรียบเหมือนอะไร?</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>สีทาบ้านและการตกแต่ง</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>เสาเข็ม</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>กุญแจบ้าน</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>coding_01_L2_01</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>coding_01</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>แท็ก &lt;h1&gt; ใช้ทำอะไร?</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>แทรกรูปภาพ</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>สร้างตาราง</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>หัวข้อใหญ่</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>coding_01_L3_01</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>coding_01</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>อยากเปลี่ยน 'สีตัวอักษร' บนเว็บ ควรไปแก้ที่ส่วนใด?</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ไฟล์เพลง</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>เครื่องพิมพ์</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>coding_02_L1_01</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>coding_02</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C7" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>คำสั่งใดใช้แสดงผลข้อความใน Python?</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>echo("Hello")</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>print("Hello")</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>console.log("Hello")</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>วาดรูปงู</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>coding_02_L1_02</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>coding_02</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C8" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Python แบ่งบล็อกโค้ดด้วยอะไร?</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ภาษา Python ตั้งชื่อตามอะไร?</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>งูหลามยักษ์</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ชื่อลูกสาวผู้สร้าง</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>คณะตลก Monty Python</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>coding_02_L2_01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>coding_02</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Python ใช้อะไรแบ่งบล็อกโค้ด?</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>การย่อหน้า (indent)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>เครื่องหมาย ;</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>วงเล็บปีกกา { }</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>เครื่องหมาย ;</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>การย่อหน้า (indent)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr"/>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>coding_02_L3_01</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>coding_02</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>จุดเด่นที่ทำให้คนนิยม Python คือข้อใด?</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ทำงานได้เฉพาะบนมือถือ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>อ่านง่าย เขียนเข้าใจง่าย</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ไม่ต้องพิมพ์โค้ดเลย</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>coding_03_L1_01</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>coding_03</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>JavaScript ทำให้หน้าเว็บทำอะไรได้?</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>โต้ตอบกับผู้ใช้ได้</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>พิมพ์งานลงกระดาษ</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ประกอบคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>coding_03_L1_02</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>coding_03</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>JavaScript ทำงานโดยตรงในที่ใด?</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>เครื่องซักผ้า</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>เครื่องคิดเลข</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>เบราว์เซอร์</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>coding_02_L2_01</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>coding_02</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>coding_03_L2_01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>coding_03</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>ข้อใดคือ list ใน Python?</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>x = [1, 2, 3]</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>x = (1, 2, 3)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>x = {"a": 1}</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ข้อใดคือตัวอย่างงานของ JavaScript?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>กดปุ่มแล้วมีข้อความเด้งขึ้นมา</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ต่อสายไฟเข้าเมนบอร์ด</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>รีดผ้า</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="J5" s="3" t="n">
+      <c r="J13" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>coding_02_L3_01</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>coding_02</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>coding_03_L3_01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>coding_03</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>3</v>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>ผลลัพธ์ของ print(len("CodeCoin")) คืออะไร?</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>คำสั่งแสดงผลใน console ของ JavaScript คือ?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>print()</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>console.log()</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J14" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>coding_04_L1_01</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>coding_04</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SQL คือภาษาสำหรับจัดการอะไร?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>รูปภาพ</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ฐานข้อมูล</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>เสียงเพลง</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>coding_04_L1_02</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>coding_04</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>อยาก 'ดึงข้อมูล' มาดู ใช้คำสั่งใด?</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>COPY-PASTE</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>coding_04_L2_01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>coding_04</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>อยาก 'ลบ' ข้อมูลทิ้ง ใช้คำสั่งใด?</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UPDATE</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>coding_04_L3_01</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>coding_04</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>อยาก 'เพิ่มข้อมูลใหม่' เข้าไป ใช้คำสั่งใด?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SELECT</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>design_01_L1_01</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>design_01</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>เครื่องมือที่ช่วยจับคู่สีเรียกว่าอะไร?</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ตารางธาตุ</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>วงล้อสี (Color Wheel)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>เข็มทิศสี</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>design_01_L1_02</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>design_01</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>สีคู่ตรงข้าม (Complementary) ให้ความรู้สึกแบบใด?</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>โดดเด่น สะดุดตา</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>มองไม่เห็น</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ง่วงนอน</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>design_01_L2_01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>design_01</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>สีที่อยู่ข้างเคียงกันในวงล้อสี ให้ความรู้สึกแบบใด?</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ตัดกันรุนแรง</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>กลมกลืน</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ร้อนแรง</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>design_01_L3_01</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>design_01</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>อยากให้ปุ่ม 'สมัครเลย' เด่นจากพื้นหลัง ควรเลือกสีแบบใด?</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>สีเดียวกับพื้นหลังเป๊ะ ๆ</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>สีใสมองทะลุได้</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>สีคู่ตรงข้ามกับพื้นหลัง</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>design_02_L1_01</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>design_02</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>หัวใจสำคัญของ Photoshop คือระบบอะไร?</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Layer</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pivot Table</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Socket</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>design_02_L1_02</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>design_02</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Photoshop เหมาะกับงานประเภทใด?</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>คำนวณภาษี</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ประกอบคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>ตกแต่งแก้ไขรูปภาพ</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>design_02_L2_01</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>design_02</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ไฟล์ Photoshop ที่เก็บ Layer ไว้ครบคือนามสกุลใด?</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>.JPG</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>.PSD</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>.MP3</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>design_02_L3_01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>design_02</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ข้อดีของการแยกงานเป็น Layer คืออะไร?</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>แก้ทีละส่วนได้โดยไม่กระทบส่วนอื่น</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ทำให้ไฟล์หายเร็วขึ้น</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>ป้องกันไวรัส</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>design_03_L1_01</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>design_03</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>จุดเด่นของภาพแบบเวกเตอร์ (Vector) คืออะไร?</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>ปิดเครื่องแล้วภาพหาย</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ขยายใหญ่แค่ไหนก็ไม่แตก</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>ใช้ได้เฉพาะสีดำ</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>design_03_L1_02</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>design_03</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Illustrator เหมาะกับงานประเภทใดที่สุด?</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ออกแบบโลโก้</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ทำบัญชีรายรับรายจ่าย</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>ลงวินโดวส์</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>design_03_L2_01</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>design_03</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ภาพที่ซูมเข้าไปแล้ว 'แตกเป็นเม็ด ๆ' คือภาพแบบใด?</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>เวกเตอร์ (Vector)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>สามมิติ</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>พิกเซล (Raster)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>design_03_L3_01</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>design_03</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ไฟล์งานหลักของ Illustrator คือนามสกุลใด?</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>.AI</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>.XLSX</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>.EXE</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>design_04_L1_01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>design_04</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>จุดเด่นที่ทำให้ Canva ใช้ง่ายคืออะไร?</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ต้องเขียนโค้ดเป็นก่อน</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ใช้ได้เฉพาะบนกระดาษ</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>มี Template สำเร็จรูปให้เลือก</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>design_04_L1_02</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>design_04</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Canva คือเครื่องมือประเภทใด?</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>ออกแบบสื่อออนไลน์</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>โปรแกรมบัญชี</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>เกมยิงปืน</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>design_04_L2_01</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>design_04</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ก่อนเริ่มออกแบบโพสต์ ควรเลือกอะไรให้ตรงกับแพลตฟอร์ม?</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>สีของเมาส์</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ขนาดของชิ้นงาน</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>ยี่ห้อคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>design_04_L3_01</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>design_04</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>โพสต์ IG แบบ 'สี่เหลี่ยมจัตุรัส' หมายความว่าอย่างไร?</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>กว้างมากกว่าสูง 2 เท่า</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>เป็นวงกลม</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>ด้านกว้างเท่ากับด้านสูง</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>office_01_L1_01</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>office_01</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C35" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>คีย์ลัดใดใช้บันทึกไฟล์ใน Word?</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Ctrl+P</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Ctrl+S</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Ctrl+V</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
-      <c r="I7" s="3" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alt+F4</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>office_01_L1_02</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>office_01</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C36" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>การสร้างสารบัญอัตโนมัติต้องใช้อะไรก่อน?</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Word เหมาะกับงานประเภทใด?</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>พิมพ์เอกสารและรายงาน</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ตัดต่อเพลง</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>แต่งรูปหน้าใส</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>office_01_L2_01</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>office_01</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>อยากสร้างสารบัญอัตโนมัติ ต้องใช้อะไรกับหัวข้อก่อน?</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
         <is>
           <t>ตัวหนา (Bold)</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ขีดเส้นใต้</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>Style (Heading)</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>เปลี่ยนฟอนต์</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>office_01_L3_01</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>office_01</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ทำไมควรใช้ Heading แทนการทำตัวหนาเอง?</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>สร้างสารบัญอัตโนมัติได้</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ทำให้ไฟล์เป็นความลับ</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ประหยัดหมึกพิมพ์</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>office_02_L1_01</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>office_02</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>สูตรใน Excel ต้องขึ้นต้นด้วยเครื่องหมายใดเสมอ?</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t># (ชาร์ป)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>= (เท่ากับ)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>? (คำถาม)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>design_02_L1_01</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>design_02</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>office_02_L1_02</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>office_02</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>ไฟล์ Photoshop ที่เก็บ Layer ครบคือนามสกุลใด?</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>.JPG</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>.PSD</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>.PNG</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>สูตรหา 'ผลรวม' ใน Excel คือสูตรใด?</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>RUN</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>JUMP</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>office_02_L2_01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>office_02</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>สูตรหา 'ค่าเฉลี่ย' ใน Excel คือสูตรใด?</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>COUNT</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>AVERAGE</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>office_02_L3_01</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>office_02</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>สูตร =SUM(A1:A10) หมายถึงอะไร?</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>รวมค่าตั้งแต่ช่อง A1 ถึง A10</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ลบช่อง A1 ทิ้ง 10 ครั้ง</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>ระบายสีช่อง A1</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>office_03_L1_01</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>office_03</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pivot Table ช่วยทำอะไรได้?</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>สรุปข้อมูลจำนวนมากได้รวดเร็ว</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>วาดการ์ตูน</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>ซ่อมคอมพิวเตอร์</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>office_03_L1_02</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>office_03</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ข้อดีของ Pivot Table คืออะไร?</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ทำให้คอมเร็วขึ้น</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>สรุปข้อมูลได้โดยไม่ต้องเขียนสูตรเอง</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>กันไวรัสได้</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>office_03_L2_01</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>office_03</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Pivot Table สร้างได้จากเมนูใด?</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Insert</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Delete</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Shut Down</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>office_03_L3_01</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>office_03</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>งานแบบใดเหมาะกับ Pivot Table ที่สุด?</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>แต่งรูปโปรไฟล์</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>เขียนหน้าเว็บ</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>สรุปยอดขายรายเดือนจากข้อมูลดิบเป็นพันแถว</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>office_04_L1_01</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>office_04</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>สไลด์นำเสนอที่ดีควรเป็นแบบใด?</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>อัดข้อความให้แน่นทุกบรรทัด</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ข้อความน้อย เน้นภาพและคีย์เวิร์ด</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>ใช้ฟอนต์เล็กที่สุดเท่าที่ทำได้</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>office_04_L1_02</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>office_04</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PowerPoint ใช้ทำอะไรเป็นหลัก?</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>นำเสนองาน</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>คำนวณสูตร</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>แต่งเพลง</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>office_04_L2_01</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>office_04</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>คีย์ลัดที่ใช้เริ่มพรีเซนต์คือปุ่มใด?</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Esc</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Delete</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>office_04_L3_01</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>office_04</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>กฎ 6x6 ของการทำสไลด์หมายถึงอะไร?</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ไม่เกิน 6 บรรทัดต่อสไลด์ และ 6 คำต่อบรรทัด</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ต้องใช้ 6 สีใน 6 สไลด์</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>ต้องพรีเซนต์ให้ครบ 66 นาที</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>hardware_01_L1_01</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>hardware_01</t>
         </is>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="C51" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CPU เปรียบเสมือนอวัยวะใดของคอมพิวเตอร์?</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>หัวใจ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>สมอง</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>กระเพาะ</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>hardware_01_L1_02</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hardware_01</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>CPU ติดตั้งลงบนส่วนใดของเมนบอร์ด?</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Socket</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>RAM Slot</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>SATA Port</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr"/>
-      <c r="I10" s="3" t="inlineStr">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ที่วางแก้วน้ำ</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>DRAFT_ตัวอย่างแถวร่าง</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>coding_01</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>hardware_01_L2_01</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>hardware_01</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ก่อนซื้อ CPU กับเมนบอร์ด ต้องเช็คอะไรให้ตรงกัน?</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>สีของกล่อง</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ยี่ห้อจอภาพ</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Socket</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>hardware_01_L3_01</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>hardware_01</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ถ้า Socket ของ CPU กับเมนบอร์ดไม่ตรงกัน จะเกิดอะไรขึ้น?</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>ติดตั้งไม่ได้</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>เครื่องเร็วขึ้น 2 เท่า</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ไม่มีผลอะไรเลย</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>hardware_02_L1_01</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>hardware_02</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>DRAFT ใส่โจทย์ที่ยังไม่เสร็จแบบนี้ ระบบจะข้ามให้</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr"/>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr"/>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>เมื่อปิดเครื่อง ข้อมูลใน RAM จะเป็นอย่างไร?</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>ถูกเก็บถาวร</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>หายไป</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>กลายเป็นไฟล์เพลง</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>hardware_02_L1_02</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>hardware_02</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>อุปกรณ์ที่เก็บข้อมูลแบบ 'ถาวร' คือข้อใด?</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SSD / HDD</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>RAM</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>พัดลมเคส</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>hardware_02_L2_01</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>hardware_02</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ทำไม SSD ถึงเร็วกว่า HDD?</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>มีสีสวยกว่า</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ราคาถูกกว่า</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>ไม่มีจานหมุนข้างใน</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>hardware_02_L3_01</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>hardware_02</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>3</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>RAM ทำหน้าที่อะไร?</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>หน่วยความจำชั่วคราวขณะเครื่องทำงาน</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>จ่ายไฟให้ทุกชิ้นส่วน</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>แสดงภาพขึ้นจอ</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>hardware_03_L1_01</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>hardware_03</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Power Supply (PSU) ทำหน้าที่อะไร?</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>เก็บไฟล์งาน</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>จ่ายไฟให้ทุกชิ้นส่วนในเครื่อง</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>เป่าลมเย็น</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>hardware_03_L1_02</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>hardware_03</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>การเลือกซื้อ PSU ต้องดูอะไรเป็นหลัก?</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>กำลังวัตต์พอกับอุปกรณ์</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>น้ำหนักเบาที่สุด</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>มีไฟ RGB สวย ๆ</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>hardware_03_L2_01</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>hardware_03</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ถ้าต่อสายไฟผิดช่อง ผลที่พบบ่อยคืออะไร?</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>เครื่องแรงขึ้น</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ได้ Wi-Fi ฟรี</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>เครื่องไม่ติด</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>hardware_03_L3_01</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>hardware_03</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>สายไฟเส้นใหญ่ที่สุดที่เสียบเข้าเมนบอร์ดโดยตรงคือสายใด?</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>สาย 24-pin</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>สาย LAN</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>สายหูฟัง</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>hardware_04_L1_01</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>hardware_04</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ก่อนใส่เมนบอร์ดลงเคส นิยมติดตั้งอะไรลงบนเมนบอร์ดก่อน?</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>การ์ดจอ</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>CPU และ RAM</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>สติกเกอร์</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>hardware_04_L1_02</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>hardware_04</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ขั้นตอน 'สุดท้าย' หลังประกอบเครื่องเสร็จคืออะไร?</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>ลงวินโดวส์</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ถอด CPU ออกมาเช็ด</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>ทาสีเคสใหม่</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>hardware_04_L2_01</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>hardware_04</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>การลงวินโดวส์นิยมทำผ่านอุปกรณ์ใด?</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>แผ่นเสียง</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>สายหูฟัง</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>USB Boot</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>hardware_04_L3_01</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>hardware_04</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>ทำไมจึงติด CPU + RAM นอกเคสก่อน?</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>พื้นที่กว้าง ทำงานง่ายกว่า</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ทำให้เครื่องแรงขึ้น</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>เป็นกฎหมายบังคับ</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>30</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/codecoin_database.xlsx
+++ b/codecoin_database.xlsx
@@ -4563,189 +4563,678 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>โจทย์ Debug ช่องติดบั๊ก (เป้า: 10-15 ข้อ) | code_snippet ขึ้นบรรทัดใหม่ด้วย Alt+Enter | answer กรอก a/b/c | time_limit วินาที</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>โจทย์ "หาจุดผิด" ช่องติดบั๊ก ครบ 4 วิชา (เป้า: 10-15 ข้อ) | code_snippet = โค้ดหรือสถานการณ์ ขึ้นบรรทัดใหม่ด้วย Alt+Enter | answer กรอก a/b/c | ทุกข้อระดับง่าย 30 วิ</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>bug_id</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>code_snippet</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>question_th</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>choice_a</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>choice_b</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>choice_c</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>time_limit</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>bug_01</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>for i in range(5)
-    print(i)</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pritn("Hello")</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>โค้ดนี้ error เพราะอะไร?</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>ใช้ range ไม่ได้</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>ลืมใส่ : ท้ายบรรทัด for</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>ต้องใช้ printf</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>b</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="n">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>พิมพ์คำสั่ง print ผิดเป็น pritn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ห้ามใช้คำว่า Hello</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ต้องเขียนเป็นภาษาไทยเท่านั้น</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>bug_02</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>nane = "Ball"
 print(name)</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>โค้ดนี้ error เพราะอะไร?</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>ประกาศตัวแปรผิดชื่อ (nane ≠ name)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>print ใช้กับตัวแปรไม่ได้</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ตั้งชื่อตัวแปรไม่ตรงกัน (nane ≠ name)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>ต้องใส่ ; ท้ายบรรทัด</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bug_03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>print("สวัสดีครับ)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>โค้ดนี้ error เพราะอะไร?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ข้อความยาวเกินไป</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ห้ามใช้วงเล็บกับ print</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ลืมปิดเครื่องหมายคำพูด " ท้ายข้อความ</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bug_04</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>&lt;img scr="photo.jpg"&gt;</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ทำไมรูปภาพไม่ขึ้นบนหน้าเว็บ?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ไฟล์ต้องเป็น .png เท่านั้น</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>พิมพ์ scr ผิด ที่ถูกต้องคือ src</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>รูปใหญ่เกินไป</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bug_05</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>พิมพ์สูตรในช่อง Excel:
+SUM(A1:A10)
+แต่ช่องแสดงเป็นข้อความ ไม่ยอมคำนวณ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>อะไรผิด?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ช่อง A1 ถึง A10 ห้ามมีตัวเลข</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>คอมพิวเตอร์เครื่องนี้บวกเลขไม่เป็น</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>สูตรลืมขึ้นต้นด้วยเครื่องหมาย =</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bug_06</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>พิมพ์สูตรหาค่าเฉลี่ย:
+=AVREAGE(A1:A5)
+Excel ขึ้น #NAME?</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>อะไรผิด?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>พิมพ์ AVERAGE ผิดเป็น AVREAGE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>หาค่าเฉลี่ยได้ครั้งละ 3 ช่องเท่านั้น</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Excel ไม่รองรับค่าเฉลี่ย</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H8" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>bug_03</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>x = "5"
-y = x + 3
-print(y)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>โค้ดนี้ error เพราะอะไร?</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>บวกเลขเกิน 2 ตัวไม่ได้</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>เอา string มาบวกกับตัวเลขไม่ได้</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>ต้องประกาศ y ก่อน</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bug_07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>อยากบันทึกไฟล์ Word
+เลยกด Ctrl+P
+แต่หน้าสั่งพิมพ์เด้งขึ้นมาแทน</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>อะไรผิด?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>กดคีย์ลัดผิด — บันทึกไฟล์ต้องกด Ctrl+S</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>เครื่องพิมพ์เสีย</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Word บันทึกไฟล์ไม่ได้ ต้องจดใส่กระดาษ</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>bug_08</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>สไลด์นำเสนอ 1 แผ่น
+อัดข้อความแน่น 20 บรรทัด
+ฟอนต์เล็กจิ๋ว คนดูอ่านไม่ทัน</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>อะไรผิด?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>คนดูสายตาไม่ดีกันทั้งห้อง</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ข้อความเยอะเกินไป — สไลด์ที่ดีต้องข้อความน้อย เน้นภาพ</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ควรเปลี่ยนเป็นฟอนต์สีแดงจะได้อ่านง่าย</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H10" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>bug_09</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ส่งไฟล์งานให้ลูกค้าเป็น .JPG
+ลูกค้าขอแก้ข้อความในภาพ
+แต่แก้ไม่ได้แล้ว</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>อะไรผิด?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ลูกค้าใช้คอมผิดยี่ห้อ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ไฟล์ .JPG แก้ได้เฉพาะวันเสาร์</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ควรเก็บไฟล์ต้นฉบับ .PSD ที่ยังมี Layer ไว้แก้ไข</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>bug_10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>เอาโลโก้ขนาดเล็ก ๆ
+ไปขยายพิมพ์ป้ายใหญ่หน้าร้าน
+ภาพแตกเป็นเม็ด ๆ</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>อะไรผิด?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ใช้ภาพแบบพิกเซล — งานที่ต้องขยายใหญ่ควรทำเป็นเวกเตอร์</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ป้ายหน้าร้านใหญ่เกินกฎหมายกำหนด</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>สีของโลโก้ไม่สวย</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>bug_11</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ทำโปสเตอร์ตัวหนังสือสีเหลืองอ่อน
+บนพื้นหลังสีขาว
+คนบ่นว่าอ่านไม่ออกเลย</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>อะไรผิด?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>คนอ่านยืนไกลเกินไป</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>สีตัวอักษรกลืนกับพื้นหลัง — ควรใช้สีที่ตัดกันชัดเจน</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ฟอนต์ภาษาไทยอ่านยากทุกแบบ</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>bug_12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ออกแบบโพสต์ IG
+แต่เลือกขนาดแนวนอนยาวแบบป้ายโฆษณา
+พอโพสต์จริงภาพโดนครอปขอบหาย</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>อะไรผิด?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>IG ไม่รองรับรูปภาพ</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>อัปโหลดตอนเที่ยงคืนภาพเลยโดนตัด</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>เลือกขนาดชิ้นงานไม่ตรงกับแพลตฟอร์ม</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>bug_13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ประกอบคอม: ใส่ CPU ✓ ใส่ RAM ✓
+ใส่การ์ดจอ ✓ ปิดฝาเคส ✓
+กดปุ่มเปิด… เงียบสนิท ไฟไม่ติดสักดวง</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>น่าจะลืมอะไร?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ลืมต่อสายไฟจาก Power Supply</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ลืมติดสติกเกอร์ข้างเคส</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>คอมยังไม่ตื่น ต้องรอตอนเช้า</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>bug_14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>เพื่อนบอก "งานอยู่ใน RAM แล้ว
+ปิดเครื่องได้เลย ไม่ต้องเซฟ"
+พอเปิดเครื่องใหม่ งานหายหมด</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>อะไรผิด?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ไฟล์งานโดนขโมย</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAM เก็บข้อมูลแค่ชั่วคราว ปิดเครื่องแล้วหาย — ต้องเซฟลง SSD/HDD</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>เปิดเครื่องใหม่เร็วเกินไป</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>bug_15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ซื้อ CPU รุ่นใหม่มา
+จะใส่ลงเมนบอร์ดตัวเดิม
+แต่วางลงช่องไม่ได้ ขาไม่ตรงกัน</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>อะไรผิด?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ต้องกดให้แรงกว่านี้</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CPU ของปลอม</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Socket ของ CPU กับเมนบอร์ดไม่ตรงกัน</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>30</v>
       </c>
     </row>

--- a/codecoin_database.xlsx
+++ b/codecoin_database.xlsx
@@ -3901,655 +3901,751 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>การ์ดเหตุการณ์ (เป้า: โซนละ 8-10 ใบ) | mechanic: simple/choice/speed/chain/minigame | effect: +1500 รับ | -800 จ่าย | skip:1 ข้ามเทิร์น | all:-500 คนอื่นจ่ายทุกคน | collect:200 เก็บจากทุกคน | bet:1000:x3|safe:+300 เลือกเสี่ยง/ชัวร์ | weight เลขมาก=ออกบ่อย</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>event_id</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>zone</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>mechanic</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>title_th</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>description_th</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>effect</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>ev_coding_01</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>coding</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>simple</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>ชนะ Hackathon ระดับประเทศ!</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>ทีมของคุณคว้าแชมป์ รับเงินรางวัลไปเลย</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>+2000</t>
         </is>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>ev_coding_02</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>coding</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>simple</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>โค้ดมี bug ใน production</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>ระบบล่มกลางดึก ต้องจ้างคนช่วยแก้ด่วน</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>-800</t>
         </is>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>ev_coding_03</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>coding</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>choice</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>เข้ารอบชิง Hackathon!</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>จะทุ่มสุดตัวหรือรับรางวัลปลอบใจ?</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>bet:1000:x3|safe:+300</t>
         </is>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>ev_coding_04</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>coding</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>chain</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>เขียน Library แจกฟรีจนดัง</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>ทุกคนต้องจ่ายค่า support ให้คุณ</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>collect:200</t>
         </is>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>ev_coding_05</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>coding</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>simple</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Push โค้ดไม่ทัน deadline</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>โดนหักค่าปรับจากลูกค้า</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>-500</t>
         </is>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>ev_office_01</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>office</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>simple</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>นำเสนองานดีเยี่ยม</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>หัวหน้าปลื้มมาก ให้โบนัสพิเศษ</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>+1000</t>
         </is>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>ev_office_02</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>office</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>simple</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>ลืม save ไฟล์งานด่วน</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>ต้องนั่งทำใหม่ทั้งหมด เสียเวลา 1 เทิร์น</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>skip:1</t>
         </is>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>ev_office_03</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>office</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>chain</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>ทำ Template สวยจนบริษัทซื้อ</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>เก็บค่าลิขสิทธิ์จากทุกคน</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>collect:150</t>
         </is>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>ev_office_04</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>office</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>simple</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>สูตร Excel ผิดทำรายงานพัง</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>ต้องจ่ายค่าเสียหาย</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>-600</t>
         </is>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ev_office_05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>office</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>คู่แข่งทาบทามซื้อตัว!</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>จะเสี่ยงย้ายไปบริษัทใหม่ หรือรับโบนัสรั้งตัวแบบชัวร์ ๆ?</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>bet:1000:x3|safe:+300</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>ev_design_01</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>design</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>simple</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>ชนะประกวดออกแบบระดับชาติ</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>ผลงานของคุณคว้ารางวัลใหญ่</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>+1800</t>
         </is>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G13" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>ev_design_02</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>design</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>simple</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>ผลงานถูกก็อปไปประกวด</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>เสียทั้งงานเสียทั้งใจ</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>-1000</t>
         </is>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G14" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>ev_design_03</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>design</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>simple</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>ลูกค้าสั่งแก้งานใหม่ทั้งหมด</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>นั่งแก้ยาว ๆ ข้าม 1 เทิร์น</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>skip:1</t>
         </is>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G15" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>ev_design_04</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>design</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>chain</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>สไตล์งานเป็นกระแส</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>ทุกคนแย่งกันจ้างคุณ</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>collect:200</t>
         </is>
       </c>
-      <c r="G15" s="3" t="n">
+      <c r="G16" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ev_design_05</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>design</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>choice</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>งานด่วนจากลูกค้ารายใหญ่</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>เดดไลน์โหดมาก จะรับงานเสี่ยงรวย หรือคิดค่าปรึกษาเบา ๆ แล้วปล่อยผ่าน?</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>bet:800:x3|safe:+300</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>ev_hardware_01</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>hardware</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>simple</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>ประกอบเครื่องขายได้ราคาดี</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>กำไรงามจากการประกอบคอมให้ลูกค้า</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>+1500</t>
         </is>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G18" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>ev_hardware_02</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>hardware</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>simple</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>ไฟกระชากเครื่องพัง</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>ต้องซื้ออะไหล่ใหม่ยกชุด</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>-1200</t>
         </is>
       </c>
-      <c r="G17" s="3" t="n">
+      <c r="G19" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>ev_hardware_03</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>hardware</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>chain</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>ไวรัสระบาดในระบบ!</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>ทุกคนโดนหมด ยกเว้นคุณที่ลงแอนตี้ไวรัสไว้</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>all:-500</t>
         </is>
       </c>
-      <c r="G18" s="3" t="n">
+      <c r="G20" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>ev_hardware_04</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>hardware</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>choice</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>ได้ของแถมจากงาน Computex</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>จะเก็งกำไรหรือขายทิ้งเลย?</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>bet:1000:x3|safe:+300</t>
         </is>
       </c>
-      <c r="G19" s="3" t="n">
+      <c r="G21" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ev_hardware_05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>hardware</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>simple</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>เพื่อนฝากจัดสเปกคอมเล่นเกม</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>จัดสเปกคุ้มจนเพื่อนปลื้ม ได้ค่านายหน้า</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>+800</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/codecoin_database.xlsx
+++ b/codecoin_database.xlsx
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -4295,7 +4295,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -4610,7 +4610,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">

--- a/codecoin_database.xlsx
+++ b/codecoin_database.xlsx
@@ -3961,7 +3961,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>speed</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>speed</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>speed</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4659,7 +4659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4710,6 +4710,16 @@
           <t>time_limit</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>difficulty</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>hint</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4750,6 +4760,16 @@
       <c r="H3" t="n">
         <v>30</v>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ลองสะกดคำสั่งอีกครั้งให้ดี ๆ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4791,6 +4811,16 @@
       <c r="H4" t="n">
         <v>30</v>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>เทียบชื่อตัวแปรบรรทัดแรกกับตอนที่ใช้ print ว่าตรงกันไหม</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4831,6 +4861,16 @@
       <c r="H5" t="n">
         <v>30</v>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>นับเครื่องหมายคำพูด " ว่าเปิด-ปิดครบคู่หรือยัง</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4870,6 +4910,16 @@
       </c>
       <c r="H6" t="n">
         <v>30</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ดูตัวสะกดของคำที่ใช้ใส่ path รูปภาพให้ดี</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4913,6 +4963,16 @@
       <c r="H7" t="n">
         <v>30</v>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>สูตร Excel ทุกสูตรต้องขึ้นต้นด้วยอะไร</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4955,6 +5015,16 @@
       <c r="H8" t="n">
         <v>30</v>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>เทียบตัวสะกดชื่อฟังก์ชันกับชื่อที่ถูกต้อง</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4997,6 +5067,16 @@
       <c r="H9" t="n">
         <v>30</v>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>คีย์ลัดสำหรับบันทึกไฟล์คือ Ctrl+ อะไร</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5039,6 +5119,16 @@
       <c r="H10" t="n">
         <v>30</v>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ลองนับจำนวนบรรทัดข้อความในสไลด์ดู</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5081,6 +5171,16 @@
       <c r="H11" t="n">
         <v>30</v>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>ไฟล์ที่ยังแก้ไข Layer ได้ควรเป็นนามสกุลอะไร</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5123,6 +5223,16 @@
       <c r="H12" t="n">
         <v>30</v>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ภาพแบบพิกเซลกับเวกเตอร์ ขยายใหญ่แล้วต่างกันยังไง</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5165,6 +5275,16 @@
       <c r="H13" t="n">
         <v>30</v>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ลองนึกภาพสีเหลืองอ่อนบนพื้นขาว มองเห็นชัดไหม</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5207,6 +5327,16 @@
       <c r="H14" t="n">
         <v>30</v>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>แต่ละแพลตฟอร์มมีสัดส่วนภาพที่แนะนำต่างกัน</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5249,6 +5379,16 @@
       <c r="H15" t="n">
         <v>30</v>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>เช็คว่าสายไฟจากแหล่งจ่ายไฟต่อเข้าเมนบอร์ดครบหรือยัง</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5291,6 +5431,16 @@
       <c r="H16" t="n">
         <v>30</v>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>RAM กับ SSD/HDD เก็บข้อมูลต่างกันตรงไหน</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5332,6 +5482,16 @@
       </c>
       <c r="H17" t="n">
         <v>30</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>easy</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>CPU กับเมนบอร์ดต้องมีอะไรตรงกันถึงจะใส่ลงได้</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/codecoin_database.xlsx
+++ b/codecoin_database.xlsx
@@ -1172,7 +1172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3888,6 +3888,694 @@
       </c>
       <c r="J66" t="n">
         <v>30</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>coding_01_L4_01</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>coding_01</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ทำไมนักพัฒนาแนะนำให้ใช้แท็ก &lt;nav&gt;, &lt;header&gt;, &lt;footer&gt; แทนการใช้ &lt;div&gt; ล้วน ๆ ทั้งหน้า?</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>เพราะแท็กเหล่านี้สวยกว่า &lt;div&gt; เวลาเปิดดูโค้ด</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>เพราะแท็กความหมาย (semantic) ช่วยให้เบราว์เซอร์/SEO/โปรแกรมอ่านหน้าจอเข้าใจโครงสร้างหน้าเว็บได้ดีกว่า</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>เพราะ &lt;div&gt; ใช้กับ CSS ไม่ได้</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>coding_02_L4_01</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>coding_02</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>4</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>เขียนฟังก์ชันที่พยายามแก้ค่าตัวแปร x ไว้ข้างในฟังก์ชัน แต่พอออกมาดูค่า x ข้างนอกกลับไม่เปลี่ยน สาเหตุน่าจะเป็นอะไร?</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ตัวแปรที่สร้างในฟังก์ชันเป็นตัวแปร local แยกขอบเขตจากตัวแปร x ข้างนอก (global)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Python มีบั๊ก ไม่สามารถแก้ค่าตัวแปรได้</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>ต้องปิดโปรแกรมแล้วเปิดใหม่ค่าจึงจะอัปเดต</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>coding_03_L4_01</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>coding_03</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>โค้ด JavaScript เทียบค่า if (x == "5") ทำงานผิดจากที่ตั้งใจ เพราะ x เป็นตัวเลข 5 ไม่ใช่ข้อความ ควรแก้เป็นตัวดำเนินการใด?</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>== เหมือนเดิม ใช้ได้ทุกกรณี</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>=== (strict equality) เพราะเทียบทั้งค่าและชนิดข้อมูล ไม่แปลงชนิดให้อัตโนมัติ</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>= เพราะเป็นการกำหนดค่าที่ถูกต้องกว่า</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>coding_04_L4_01</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>coding_04</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>4</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>ต้องการดึงข้อมูลนักเรียนที่อยู่ใน 2 ตาราง (ตารางชื่อ และตารางคะแนน) มาแสดงพร้อมกันโดยเชื่อมด้วยรหัสนักเรียนเดียวกัน ควรใช้คำสั่งใด?</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>JOIN</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>design_01_L4_01</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>design_01</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>4</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>อยากให้คนที่มีปัญหาการมองเห็นสีอ่านข้อความบนเว็บได้ง่ายขึ้น ควรให้ความสำคัญกับอะไรระหว่างสีตัวอักษรกับพื้นหลัง?</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ค่าความต่างของความสว่าง/คอนทราสต์ (Contrast Ratio) ระหว่างสีตัวอักษรกับพื้นหลัง</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ต้องใช้สีโทนร้อนเท่านั้น</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>ต้องใช้ตัวอักษรตัวหนาแทนการเลือกสี</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>design_02_L4_01</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>design_02</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>4</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>อยากลบพื้นหลังออกจากภาพใน Photoshop แต่ไม่อยากให้เนื้อภาพต้นฉบับเสียหายถาวร ควรใช้เครื่องมือใด?</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Eraser Tool ลบทิ้งไปเลย</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Layer Mask ซ่อนบางส่วนของภาพโดยไม่ลบข้อมูลจริง แก้กลับได้ทีหลัง</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ลบไฟล์แล้ววาดใหม่ทั้งหมด</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>design_03_L4_01</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>design_03</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>4</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ทำไมโลโก้บริษัทมักถูกส่งมอบเป็นไฟล์เวกเตอร์ (.AI/.EPS) แทนที่จะเป็น .JPG ทั้งที่หน้าตาภาพดูเหมือนกัน?</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>ไฟล์เวกเตอร์นำไปใช้ขยาย/ย่อในสื่อทุกขนาดได้โดยไม่แตก ต่างจาก .JPG ที่เป็นภาพพิกเซล</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>.AI เปิดได้เร็วกว่า .JPG เท่านั้น</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>ไฟล์ .JPG ไม่สามารถมีโลโก้ได้</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>design_04_L4_01</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>design_04</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>4</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ต้องการนำโลโก้ที่ออกแบบใน Canva ไปวางซ้อนบนภาพอื่นโดยไม่ให้มีพื้นหลังสี่เหลี่ยมติดมาด้วย ควร Export เป็นไฟล์แบบใด?</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>PNG แบบพื้นหลังโปร่งใส (Transparent Background)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>JPG ธรรมดา</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>PDF สำหรับพิมพ์</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>office_01_L4_01</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>office_01</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>4</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>ต้องพิมพ์จดหมายเชิญแบบเดียวกัน 50 ฉบับ ให้คนละชื่อผู้รับ โดยไม่อยากพิมพ์ทีละฉบับ ควรใช้ฟีเจอร์ใดของ Word?</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Mail Merge (จดหมายเวียน) ดึงรายชื่อจากไฟล์ข้อมูลมาใส่อัตโนมัติ</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Track Changes</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Find and Replace</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>office_02_L4_01</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>office_02</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>4</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>อยากให้ Excel เขียนคำว่า "ผ่าน" ถ้าคะแนนในช่อง A1 มากกว่า 50 และเขียน "ไม่ผ่าน" ถ้าน้อยกว่า ควรใช้ฟังก์ชันใด?</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>=SUM(A1)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>=IF(A1&gt;50,"ผ่าน","ไม่ผ่าน")</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>=AVERAGE(A1)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>office_03_L4_01</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>office_03</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>มีข้อมูลยอดขายรายวันทั้งปี อยากสรุปเป็นยอดขายรายไตรมาส (Q1-Q4) ใน Pivot Table ควรทำอย่างไร?</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>พิมพ์สูตรคำนวณแยกทีละแถวด้วยมือ</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>จัดกลุ่ม (Group) ฟิลด์วันที่ในพื้นที่ Row เป็นช่วงไตรมาส</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>ลบข้อมูลที่ไม่ใช่ไตรมาสแรกทิ้ง</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>office_04_L4_01</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>office_04</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>4</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>อยากซ้อมพรีเซนต์แล้วให้ PowerPoint จับเวลาที่ใช้พูดในแต่ละสไลด์ให้อัตโนมัติ ควรใช้ฟีเจอร์ใด?</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Rehearse Timings (ในแท็บ Slide Show)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Track Changes</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Mail Merge</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>hardware_01_L4_01</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>hardware_01</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>4</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>ซื้อ CPU รุ่นใหม่มา Socket ตรงกับเมนบอร์ดเป๊ะ แต่ประกอบเสร็จแล้วเปิดเครื่องไม่ติด/ไม่แสดงผล ควรตรวจสอบอะไรก่อน?</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>อัปเดต BIOS ของเมนบอร์ดให้รองรับ CPU รุ่นใหม่ (บางเมนบอร์ดรุ่นเดิมต้องอัปเดตก่อนใช้ CPU รุ่นใหม่ได้)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>เปลี่ยนไปซื้อ CPU ยี่ห้ออื่นแทน</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Socket ตรงกันแปลว่าไม่มีทางเสียได้ ต้องเป็นปัญหาไฟดับ</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>hardware_02_L4_01</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>hardware_02</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>4</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ใส่ RAM 2 แถวความจุเท่ากันแต่ความเร็ว (MHz) ต่างกันลงในเครื่องเดียวกัน จะเกิดอะไรขึ้น?</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>เครื่องเปิดไม่ติดเลยทันที</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ใช้งานได้ปกติ แต่ RAM ทั้งคู่จะทำงานที่ความเร็วเท่ากับแถวที่ช้ากว่า</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>RAM แถวที่เร็วกว่าจะทำงานเดี่ยว ๆ ส่วนอีกแถวจะถูกปิดใช้งาน</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>hardware_03_L4_01</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>hardware_03</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>4</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>ฉลาก "80+ Gold" ที่ติดอยู่บนกล่อง Power Supply บ่งบอกถึงอะไร?</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ระดับประสิทธิภาพในการแปลงไฟ (ยิ่งระดับสูง ยิ่งสูญเสียพลังงานเป็นความร้อนน้อยลง)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>สีของตัวเครื่อง Power Supply</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>จำนวนปีที่รับประกันสินค้า</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>hardware_04_L4_01</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>hardware_04</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>4</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ลง Windows เสร็จใหม่ ๆ แต่หน้าจอแสดงผลไม่คมชัด สีเพี้ยน ปรับความละเอียดจอไม่ได้ตามสเปคจริง ควรทำอะไรก่อน?</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ติดตั้ง/อัปเดตไดรเวอร์การ์ดจอ (Display Driver) ให้ตรงรุ่น</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>เปลี่ยนจอภาพใหม่ทันที</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>ถอด RAM ออกแล้วใส่กลับเข้าไป</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/codecoin_database.xlsx
+++ b/codecoin_database.xlsx
@@ -5347,7 +5347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5427,22 +5427,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>พิมพ์คำสั่ง print ผิดเป็น pritn</t>
+          <t>ต้องใช้คำสั่ง println แทน print</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ห้ามใช้คำว่า Hello</t>
+          <t>พิมพ์ชื่อคำสั่ง print ผิด</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ต้องเขียนเป็นภาษาไทยเท่านั้น</t>
+          <t>ลืมใส่เครื่องหมายคำพูดรอบ Hello</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>b</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>print ใช้กับตัวแปรไม่ได้</t>
+          <t>ชื่อตัวแปรตอนประกาศกับตอนเรียกใช้ไม่ตรงกัน</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ตั้งชื่อตัวแปรไม่ตรงกัน (nane ≠ name)</t>
+          <t>print รับได้ทีละ 1 ตัวอักษรเท่านั้น</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ต้องใส่ ; ท้ายบรรทัด</t>
+          <t>ต้องประกาศชนิดข้อมูลก่อน เช่น str name</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -5528,17 +5528,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ข้อความยาวเกินไป</t>
+          <t>ข้อความภาษาไทยต้องใส่ u นำหน้า</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ห้ามใช้วงเล็บกับ print</t>
+          <t>print ใช้กับภาษาไทยไม่ได้</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ลืมปิดเครื่องหมายคำพูด " ท้ายข้อความ</t>
+          <t>ลืมปิดเครื่องหมายคำพูดท้ายข้อความ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5578,22 +5578,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ไฟล์ต้องเป็น .png เท่านั้น</t>
+          <t>attribute src สะกดผิด</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>พิมพ์ scr ผิด ที่ถูกต้องคือ src</t>
+          <t>แท็ก img ต้องมีแท็กปิด &lt;/img&gt;</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>รูปใหญ่เกินไป</t>
+          <t>ต้องระบุความกว้าง width ทุกครั้ง</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>a</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -5630,22 +5630,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ช่อง A1 ถึง A10 ห้ามมีตัวเลข</t>
+          <t>ต้องเว้นวรรคระหว่าง SUM กับวงเล็บ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>คอมพิวเตอร์เครื่องนี้บวกเลขไม่เป็น</t>
+          <t>สูตรลืมขึ้นต้นด้วยเครื่องหมาย =</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>สูตรลืมขึ้นต้นด้วยเครื่องหมาย =</t>
+          <t>ช่วง A1:A10 กว้างเกินที่ SUM รับได้</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>b</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -5682,17 +5682,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>พิมพ์ AVERAGE ผิดเป็น AVREAGE</t>
+          <t>พิมพ์ชื่อฟังก์ชัน AVERAGE ผิด</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>หาค่าเฉลี่ยได้ครั้งละ 3 ช่องเท่านั้น</t>
+          <t>ต้องใส่เครื่องหมาย $ หน้าช่วงข้อมูล</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Excel ไม่รองรับค่าเฉลี่ย</t>
+          <t>ค่าเฉลี่ยต้องใช้ =MEAN() ไม่ใช่ AVERAGE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5734,17 +5734,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>กดคีย์ลัดผิด — บันทึกไฟล์ต้องกด Ctrl+S</t>
+          <t>บันทึกไฟล์ต้องกด Ctrl+S</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>เครื่องพิมพ์เสีย</t>
+          <t>ต้องกด Ctrl+P สองครั้งถึงจะเซฟ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Word บันทึกไฟล์ไม่ได้ ต้องจดใส่กระดาษ</t>
+          <t>ไฟล์ Word เซฟด้วยคีย์ลัดไม่ได้ ต้องใช้เมนู</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5786,17 +5786,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>คนดูสายตาไม่ดีกันทั้งห้อง</t>
+          <t>ควรเปลี่ยนเป็นฟอนต์ที่บางลงจะได้ใส่ได้ครบ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ข้อความเยอะเกินไป — สไลด์ที่ดีต้องข้อความน้อย เน้นภาพ</t>
+          <t>ข้อความเยอะเกินไป สไลด์ที่ดีควรกระชับ เน้นภาพ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ควรเปลี่ยนเป็นฟอนต์สีแดงจะได้อ่านง่าย</t>
+          <t>ควรเพิ่มจำนวนบรรทัดให้ครบ 30 จะสมดุลขึ้น</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -5838,17 +5838,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ลูกค้าใช้คอมผิดยี่ห้อ</t>
+          <t>JPG แก้ข้อความได้เฉพาะในโปรแกรมต้นทาง</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ไฟล์ .JPG แก้ได้เฉพาะวันเสาร์</t>
+          <t>ต้องส่งเป็น .JPG ความละเอียดสูงกว่านี้</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ควรเก็บไฟล์ต้นฉบับ .PSD ที่ยังมี Layer ไว้แก้ไข</t>
+          <t>ควรเก็บไฟล์ต้นฉบับที่ยังมี Layer ไว้แก้</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5890,17 +5890,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ใช้ภาพแบบพิกเซล — งานที่ต้องขยายใหญ่ควรทำเป็นเวกเตอร์</t>
+          <t>ใช้ภาพแบบพิกเซล งานที่ต้องขยายควรเป็นเวกเตอร์</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ป้ายหน้าร้านใหญ่เกินกฎหมายกำหนด</t>
+          <t>ต้องเพิ่มความสว่างของภาพก่อนขยาย</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>สีของโลโก้ไม่สวย</t>
+          <t>ไฟล์โลโก้เป็นนามสกุลที่ขยายไม่ได้</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5942,17 +5942,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>คนอ่านยืนไกลเกินไป</t>
+          <t>ตัวอักษรเล็กเกินไป ควรเพิ่มขนาดฟอนต์</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>สีตัวอักษรกลืนกับพื้นหลัง — ควรใช้สีที่ตัดกันชัดเจน</t>
+          <t>สีตัวอักษรกลืนพื้นหลัง ควรใช้สีที่ตัดกัน</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ฟอนต์ภาษาไทยอ่านยากทุกแบบ</t>
+          <t>ควรใส่เงาให้ตัวอักษรจะได้เด่นขึ้น</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>IG ไม่รองรับรูปภาพ</t>
+          <t>ต้องอัปโหลดภาพความละเอียดสูงกว่านี้</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>อัปโหลดตอนเที่ยงคืนภาพเลยโดนตัด</t>
+          <t>IG รองรับเฉพาะภาพสี่เหลี่ยมจัตุรัสเท่านั้น</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -6046,17 +6046,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ลืมต่อสายไฟจาก Power Supply</t>
+          <t>ลืมต่อสายไฟจาก Power Supply เข้าเมนบอร์ด</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ลืมติดสติกเกอร์ข้างเคส</t>
+          <t>ลืมเสียบสาย LAN เข้าเครื่อง</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>คอมยังไม่ตื่น ต้องรอตอนเช้า</t>
+          <t>ต้องกดปุ่มเปิดค้างไว้ 30 วินาที</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6098,17 +6098,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ไฟล์งานโดนขโมย</t>
+          <t>ไฟล์งานถูกโปรแกรมป้องกันไวรัสลบ</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAM เก็บข้อมูลแค่ชั่วคราว ปิดเครื่องแล้วหาย — ต้องเซฟลง SSD/HDD</t>
+          <t>RAM เก็บข้อมูลชั่วคราว ปิดเครื่องแล้วหาย ต้องเซฟลงไดรฟ์</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>เปิดเครื่องใหม่เร็วเกินไป</t>
+          <t>เปิดเครื่องใหม่เร็วเกินไป ข้อมูลเลยไม่ทันโหลด</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ต้องกดให้แรงกว่านี้</t>
+          <t>ต้องกดให้แรงและตรงกว่านี้</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CPU ของปลอม</t>
+          <t>ต้องอัปเดตไดรเวอร์ CPU ก่อนติดตั้ง</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -6179,6 +6179,211 @@
       <c r="J17" t="inlineStr">
         <is>
           <t>CPU กับเมนบอร์ดต้องมีอะไรตรงกันถึงจะใส่ลงได้</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>bug_16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>UPDATE students
+SET score = 100</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>รันคำสั่งนี้แล้วคะแนนของนักเรียน "ทุกคน" กลายเป็น 100 หมด ทั้งที่ตั้งใจแก้แค่คนเดียว อะไรผิด?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SELECT ต้องมาก่อน UPDATE เสมอ</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ลืมใส่ WHERE ระบุว่าจะแก้แถวไหน คำสั่งเลยอัปเดตทุกแถวในตาราง</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ต้องพิมพ์ SCORE เป็นตัวพิมพ์ใหญ่เท่านั้น</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>45</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>คำสั่งที่แก้ข้อมูล ถ้าไม่ระบุเงื่อนไขว่าแถวไหน จะมีผลกับกี่แถวในตาราง?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>bug_17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>สูตรช่อง B2: =A2*C1 (อัตราภาษี)
+ลาก (fill down) ไปถึง B10
+ผลลัพธ์แถวล่าง ๆ ผิดเพี้ยนทุกแถว</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ทำไมลากสูตรลงแล้วค่าผิด?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ต้องใส่ $ ล็อกตำแหน่ง C1 เป็น $C$1 (absolute reference) ไม่ให้ขยับตอนลากสูตร</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Excel ลากสูตรต่อได้ไม่เกิน 5 แถวเท่านั้น</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ต้องพิมพ์สูตรใหม่ด้วยมือทุกแถว ห้ามลากเด็ดขาด</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>45</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>ตอนลากสูตรลง ตำแหน่งอ้างอิงที่ไม่ได้ล็อกไว้จะเลื่อนตามไปด้วยทุกแถว</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>bug_18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ออกแบบโปสเตอร์ในโหมดสี RGB สีสันสดใสมากบนจอ
+พอส่งไฟล์ไปโรงพิมพ์ สีที่ได้จริงหม่นลงกว่าที่เห็นมาก</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>อะไรคือสาเหตุ?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>เครื่องพิมพ์ที่ร้านเสีย ต้องเปลี่ยนร้าน</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ต้องแปลงไฟล์เป็นโหมดสี CMYK ก่อนส่งพิมพ์ เพราะ RGB คือสีจากแสงจอ ให้เฉดสดกว่าหมึกพิมพ์จริงเสมอ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ต้องเพิ่มความสว่าง (Brightness) ของไฟล์ก่อนส่งพิมพ์</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>45</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>สีบนจอมาจากแสง ส่วนงานพิมพ์มาจากหมึก — เป็นคนละระบบสีกัน</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>bug_19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ประกอบคอมเสร็จ ต่อสาย 24-pin และ 8-pin ครบถูกช่อง
+เปิดเครื่องติดปกติ แต่พอเล่นเกมหนัก ๆ เครื่องดับตัวเองกะทันหันทุกครั้ง</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>น่าจะเป็นเพราะอะไร?</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Power Supply จ่ายไฟไม่พอ (วัตต์ต่ำเกินไป) รองรับการ์ดจอ/ซีพียูตอนโหลดหนักไม่ไหว</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>การ์ดจอ "กลัว" เกมที่มีกราฟิกสวยเกินไป</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>เป็นเพราะโปรแกรมเกมมีบั๊ก ไม่เกี่ยวกับฮาร์ดแวร์เลย</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>45</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>เครื่องดับเฉพาะตอนโหลดหนัก ลองคิดว่าอุปกรณ์ไหนต้องจ่ายไฟพุ่งสูงช่วงนั้น</t>
         </is>
       </c>
     </row>

--- a/codecoin_database.xlsx
+++ b/codecoin_database.xlsx
@@ -553,7 +553,7 @@
         <v>900</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
@@ -593,7 +593,7 @@
         <v>1000</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
@@ -633,7 +633,7 @@
         <v>1200</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>700</v>
+        <v>560</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>1400</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>800</v>
+        <v>640</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>1000</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>1200</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>700</v>
+        <v>560</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>1400</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>800</v>
+        <v>640</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         <v>1500</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>900</v>
+        <v>720</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>800</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
         <v>900</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>1000</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>1200</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>700</v>
+        <v>560</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>1500</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>900</v>
+        <v>720</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>1700</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>1800</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>1100</v>
+        <v>880</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>2000</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>1250</v>
+        <v>1000</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
